--- a/tests/fixtures/Strecnianska_v1.2_gold_TeamworkTasks.xlsx
+++ b/tests/fixtures/Strecnianska_v1.2_gold_TeamworkTasks.xlsx
@@ -40,15 +40,15 @@
     <t xml:space="preserve">STATUS</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozšírenie #1 — Ročný zálohový predpis (DNR 4.1)</t>
+    <t xml:space="preserve">4.1 Ročný zálohový predpis</t>
   </si>
   <si>
     <t xml:space="preserve">ROZŠÍRENIE Č. 1 — ROČNÝ ZÁLOHOVÝ PREDPIS (DNR sekcia 4.1)
-== 4.1.1 Biznisový účel ==
+** 4.1.1 Biznisový účel **
 Namiesto 12 mesačných faktúr vznikne na začiatku roka jeden PDF dokument — ročný zálohový predpis — ktorý slúži ako daňový doklad pre celý fakturačný rok. Obsahuje rozpis 12 rovnakých splátok so splatnosťou k definovanému dňu mesiaca. Nájomca platí 12× ročne s rovnakým variabilným symbolom; systém platby automaticky páruje (viď modul 4.2).
-== Poznámka k mesačnej fakturácii ==
+** Poznámka k mesačnej fakturácii **
 Režim ročného zálohového predpisu nahrádza mesačné faktúry pre konkrétne zmluvy. Existujúca funkcia mesačnej fakturácie zostáva v systéme pre prípadné budúce použitie, no v dennej prevádzke Družstva lekárov sa nebude bežne používať.
-== 4.1.2 Zásadné rozhodnutia ==
+** 4.1.2 Zásadné rozhodnutia **
 • Fakturačné obdobie: Vždy kalendárny rok (január — december).
 • Začiatok zmluvy v priebehu roka: Zmluvy začínajú vždy 1. dňom mesiaca. V rámci mesiaca sa nealikvotuje. Ročný predpis sa pripraví od mesiaca nástupu do decembra; od 1. januára nasledujúceho roka štandardný 12-mesačný predpis. (v1.2)
 • Obsah predpisu: Nájomné (prenajatý priestor + podiel na spoločných priestoroch) + služby spojené s nájmom (elektrina, voda/stočné, UK a TUV). Zoznam je otvorený — v budúcnosti môžu pribudnúť ďalšie položky.
@@ -63,7 +63,7 @@
 • Predčasné ukončenie zmluvy: Admin zmení dátum konca zmluvy na skutočný dátum ukončenia. Systém pri ročnom zúčtovaní započíta iba reálne odbehnuté mesiace; prípadný preplatok/nedoplatok sa vyrieši v rámci štandardného ročného zúčtovania, nie počas roka. (v1.2)
 • Preplatok z minulého roka: Preplatok sa NEPRENÁŠA do nového predpisu. Klient ho vyrovná vrátením peňazí nájomcovi mimo systém. Nájomca tak platí celý rok v plnej výške bez zníženia januárovej splátky. (v1.2)
 • Príprava a odoslanie: Dvojkrokový proces: (1) admin zvolí „Pripraviť PDF" v detaile zmluvy, skontroluje položky a sumy, (2) zvolí „Odoslať e-mailom" — PDF odoslané klientovi na e-mail evidovaný u zákazníka.
-== 4.1.3 Scenáre použitia ==
+** 4.1.3 Scenáre použitia **
 Scenár 1 — Ročné pripravenie predpisu (začiatok roka):
 1. Admin otvorí detail zmluvy a zvolí „Pripraviť ročný zálohový predpis".
 2. Systém zobrazí formulár: fakturačný rok (default = aktuálny), dátum splatnosti v mesiaci (default 5. deň aktuálneho mesiaca, prepisateľný), dátum dodania (default posledný deň mesiaca), číselný rad. (v1.2)
@@ -86,14 +86,22 @@
 15. Nájomca a družstvo sa dohodnú na predčasnom ukončení (napr. k 30. 7.). Admin zmení dátum konca zmluvy.
 16. Pôvodný ročný zálohový predpis zostáva nedotknutý; nájomca doplatí splátky podľa pôvodného plánu až do skutočného konca prenájmu.
 17. Pri ročnom zúčtovaní systém započíta iba reálne odbehnuté mesiace zmluvy. Prípadný preplatok/nedoplatok sa vyrieši cez štandardný proces ročného zúčtovania na konci roka — nie počas roka.
-== 4.1.4 Odhad pracnosti ==
-Ročný zálohový predpis: 2,5 MD (logika prípravy predpisu, formát PDF podľa vzoru SOMPET, hromadná akcia, alikvótny výpočet).</t>
+** Sumár akceptačných kritérií (z hlavných úloh) **
+• [4.1.1] V systéme pribudol nový typ dokladu „Ročný zálohový predpis", ktorý existuje popri faktúre, predfaktúre a dobropise.
+• [4.1.2] Pre každý ročný predpis vie systém zobraziť zoznam splátok s aktuálnym stavom (uhradená / čiastočne / neuhradená / preplatok).
+• [4.1.3] Pre zmluvu platnú od 1. 1. systém pripraví 12 rovnakých splátok pre celý rok.
+• [4.1.4] V detaile zmluvy je tlačidlo „Pripraviť ročný zálohový predpis".
+• [4.1.5] PDF dokument vyzerá konzistentne so vzorom SOMPET dodaným klientom.
+• [4.1.6] V zozname zmlúv je filter „Aktívne k dátumu" — admin vyberie napr. 1. 1. 2027.
+• [4.1.7] V detaile ročného zálohového predpisu je tlačidlo „Odoslať e-mailom".
+• [4.1.8] Systém má samostatný číselný rad pre ročné zálohové predpisy vo formáte ZP[YYYY]-[NNNN] (napr. ZP2026-0001).
+• [4.1.9] Pest test sada pokrýva všetky scenáre DNR 4.1.3 (Scenár 1—5).</t>
   </si>
   <si>
     <t xml:space="preserve">Active</t>
   </si>
   <si>
-    <t xml:space="preserve">Príprava systémových štruktúr pre ročný zálohový predpis</t>
+    <t xml:space="preserve">4.1.1 Príprava systémových štruktúr pre ročný zálohový predpis</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -126,7 +134,7 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">Evidencia mesačných splátok v rámci predpisu</t>
+    <t xml:space="preserve">4.1.2 Evidencia mesačných splátok v rámci predpisu</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -153,7 +161,7 @@
 - Pest `InvoiceScheduleInstallmentTest::test_status_changes_with_payments` overí prechod stavov.</t>
   </si>
   <si>
-    <t xml:space="preserve">Logika výpočtu ročného zálohového predpisu</t>
+    <t xml:space="preserve">4.1.3 Logika výpočtu ročného zálohového predpisu</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -193,7 +201,7 @@
 - Viacero rovnakých priestorov → zoskupiť per `premise_id` + `title`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Funkcia „Pripraviť ročný zálohový predpis" v detaile zmluvy</t>
+    <t xml:space="preserve">4.1.4 Funkcia „Pripraviť ročný zálohový predpis" v detaile zmluvy</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -222,7 +230,7 @@
 - Ak ostane čas — vlastný ResourceTool `nova-components/AnnualAdvancePreview` so side-by-side náhľadom pred submit.</t>
   </si>
   <si>
-    <t xml:space="preserve">PDF výstup ročného zálohového predpisu (vzor SOMPET)</t>
+    <t xml:space="preserve">4.1.5 PDF výstup ročného zálohového predpisu (vzor SOMPET)</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -272,7 +280,7 @@
 `public/css/invoice.css` — pridať `.installments` (border, padding) a `.premise-header` (light gray bg, bold).</t>
   </si>
   <si>
-    <t xml:space="preserve">Hromadné pripravenie zálohových predpisov pre všetky aktívne zmluvy</t>
+    <t xml:space="preserve">4.1.6 Hromadné pripravenie zálohových predpisov pre všetky aktívne zmluvy</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -307,7 +315,7 @@
     <t xml:space="preserve">Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">Odoslanie zálohového predpisu nájomcovi e-mailom</t>
+    <t xml:space="preserve">4.1.7 Odoslanie zálohového predpisu nájomcovi e-mailom</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -343,7 +351,7 @@
 `app/Nova/Invoice/ButtonsCard.php` — tlačidlo „Odoslať e-mailom" musí byť dostupné aj pre `type = '4'`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Číselný rad ZP a evidencia variabilných symbolov zmlúv</t>
+    <t xml:space="preserve">4.1.8 Číselný rad ZP a evidencia variabilných symbolov zmlúv</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -395,7 +403,7 @@
 - Soft-deleted zmluvy: VS sa môže reusnúť.</t>
   </si>
   <si>
-    <t xml:space="preserve">Testovanie a overenie ročného zálohového predpisu</t>
+    <t xml:space="preserve">4.1.9 Testovanie a overenie ročného zálohového predpisu</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -431,13 +439,13 @@
 ≥ 80 % na nové service triedy.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozšírenie #2 — Automatické párovanie platieb z banky (DNR 4.2)</t>
+    <t xml:space="preserve">4.2 Automatické párovanie platieb z banky</t>
   </si>
   <si>
     <t xml:space="preserve">ROZŠÍRENIE Č. 2 — AUTOMATICKÉ PÁROVANIE PLATIEB Z BANKY (DNR sekcia 4.2)
-== 4.2.1 Biznisový účel ==
+** 4.2.1 Biznisový účel **
 Klient dostáva od Tatra banky mailové notifikácie pri každom pohybe na účte. Systém raz denne načíta nové notifikácie z vyhradenej mailovej schránky, prečíta z nich sumu, variabilný symbol a dátum platby, a automaticky priradí kreditné platby k jednotlivým mesačným splátkam zálohových predpisov.
-== 4.2.2 Zásadné rozhodnutia ==
+** 4.2.2 Zásadné rozhodnutia **
 • Banka: Tatra banka, Slovakia.
 • Mailová schránka: WAME systémová — klient nepotrebuje zriaďovať žiadnu schránku ani podúčet. WAME priradí klientovi unikátnu e-mailovú adresu, ktorú si klient nastaví v internetbankingu ako cieľ notifikácií.
 • Typy platieb: Iba kredity (prichádzajúce platby). Debety (odchádzajúce platby) systém ignoruje.
@@ -449,24 +457,31 @@
 • Nerozpoznaná platba: Platba s nenalezeným VS → zaradená do zoznamu „Nespárované platby". Admin ju manuálne priradí. Bez automatických notifikácií.
 • Frekvencia spracovania: Raz denne (v nočných hodinách).
 • Počiatočný stav pri spustení systému: Pre každú zmluvu admin vytvorí jednu fiktívnu úvodnú faktúru v sume doteraz zaplatených platieb (saldo k dátumu spustenia) a k nej manuálne pridá uhrádzajúcu platbu v rovnakej sume. Týmto sa stav účtu nájomcu vyrovná a od daného dátumu systém pokračuje štandardne. (v1.2)
-== 4.2.3 Postup párovania ==
+** 4.2.3 Postup párovania **
 18. Systém raz denne načíta všetky nové e-maily zo systémovej schránky.
 19. Pre každý e-mail: overí odosielateľa (Tatra banka).
 20. Prečíta sumu, variabilný symbol, dátum pripísania a smer platby. Ak je smer = debet → preskočí.
 21. Pre kredit: nájde zmluvu s daným VS. Ak nenájde → zaradí do „Nespárované platby", platba sa neeviduje.
 22. Ak nájde: spáruje platbu s najstaršou nespárovanou splátkou danej zmluvy. Vytvorí záznam o platbe a systém automaticky prepočíta stav splátky (neuhradená → čiastočne → uhradená → preplatok). Ak je platba vyššia, prebytok sa použije na ďalšiu najstaršiu nespárovanú splátku. (v1.2)
-== 4.2.4 Práca admina ==
+** 4.2.4 Práca admina **
 • Zoznam „Bmail importy" — chronologický prehľad všetkých prichádzajúcich notifikácií s filtrom podľa stavu (spárované / nespárované / duplicita / ignorované debety).
 • Zoznam „Nespárované platby" — rýchly prehľad platieb, ktoré vyžadujú manuálny zásah. Akcia „Priradiť k zmluve" umožní adminovi vybrať zmluvu a evidovať platbu ručne.
 • Detail zmluvy zobrazuje históriu platieb — chronologický zoznam automatických aj manuálnych platieb s väzbou na pôvodný e-mail.
 • Úprava platby — admin môže existujúcu platbu upraviť (zmeniť sumu) alebo manuálne pridať novú. Slúži najmä na rozdelenie jednej veľkej platby medzi viac splátok pri nájomcoch, ktorí platia naraz za viac mesiacov. (v1.2)
-== Edge-case — platba s historickým VS ==
+** Edge-case — platba s historickým VS **
 Môže nastať situácia, kedy príde platba s variabilným symbolom, ktorý existoval v minulosti, no zmluva už nie je aktívna (napr. odsťahovaný nájomca). Takáto platba zostane v stave „Nespárovaná" a vyžaduje manuálne rozhodnutie admina. Bez ďalšej automatizácie.
-== 4.2.5 Odhad pracnosti ==
-Automatické párovanie platieb: 1,5 MD (čítanie e-mailov, rozpoznanie obsahu, priraďovacia logika, prehľady pre admina).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidencia notifikácií z banky v systéme</t>
+** Sumár akceptačných kritérií (z hlavných úloh) **
+• [4.2.1] Každá prichádzajúca notifikácia z Tatra banky sa eviduje ako záznam v systéme s pôvodným obsahom a stavom spracovania.
+• [4.2.2] V admin paneli pribudne sekcia „Bmail importy" s chronologickým prehľadom všetkých notifikácií.
+• [4.2.3] Systém sa pripojí na vyhradenú IMAP schránku, na ktorú internetbanking Tatra banky posiela notifikácie.
+• [4.2.4] Systém z textu notifikácie spoľahlivo extrahuje sumu, variabilný symbol, dátum pripísania a smer pohybu.
+• [4.2.5] Kreditná platba s rozpoznaným VS sa automaticky priradí k najstaršej nespárovanej splátke danej zmluvy.
+• [4.2.6] Systém raz denne v nočných hodinách (02:30) automaticky stiahne nové notifikácie z bankovej schránky.
+• [4.2.7] V detaile zmluvy je tab „História platieb" s chronologickým zoznamom všetkých platieb (automatických aj manuálnych) s väzbou na pôvodný e-mail.
+• [4.2.8] Pest testy pokrývajú kompletný flow: import e-mailu → parsing → párovanie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2.1 Evidencia notifikácií z banky v systéme</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -495,7 +510,7 @@
 - Index `['status', 'created_at']`, index `'parsed_variable_symbol'`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Prehľad bankových notifikácií a manuálny zásah</t>
+    <t xml:space="preserve">4.2.2 Prehľad bankových notifikácií a manuálny zásah</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -531,7 +546,7 @@
 Pridať do `NovaServiceProvider::mainMenu()` položku „Bmail importy".</t>
   </si>
   <si>
-    <t xml:space="preserve">Pripojenie systému na bankovú schránku</t>
+    <t xml:space="preserve">4.2.3 Pripojenie systému na bankovú schránku</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -584,7 +599,7 @@
 - Ops vytvorí schránku `bmail-strecnianska@reality.wame.sk` a heslo doplní do `.env`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozpoznanie obsahu notifikácie z Tatra banky</t>
+    <t xml:space="preserve">4.2.4 Rozpoznanie obsahu notifikácie z Tatra banky</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -642,7 +657,7 @@
 - Zmena formátu zo strany banky → status `parse_failed`, manuálne riešenie.</t>
   </si>
   <si>
-    <t xml:space="preserve">Automatické párovanie platieb so splátkami</t>
+    <t xml:space="preserve">4.2.5 Automatické párovanie platieb so splátkami</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -703,7 +718,7 @@
 - Platba presahujúca všetky splátky: posledná = `overpay`, zvyšok poznámka, manuálne.</t>
   </si>
   <si>
-    <t xml:space="preserve">Denné automatické sťahovanie platieb</t>
+    <t xml:space="preserve">4.2.6 Denné automatické sťahovanie platieb</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -757,7 +772,7 @@
 - Overiť že `crontab -e` na produkcii má `* * * * * cd /path &amp;&amp; php artisan schedule:run &gt;&gt; /dev/null 2&gt;&amp;1`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Manuálna úprava a rozdelenie platieb</t>
+    <t xml:space="preserve">4.2.7 Manuálna úprava a rozdelenie platieb</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -783,7 +798,7 @@
 - Akcia `AssignBmailToContract` z Task 2.2 už pokrýva manuálne pridelenie.</t>
   </si>
   <si>
-    <t xml:space="preserve">Testovanie a overenie párovania platieb</t>
+    <t xml:space="preserve">4.2.8 Testovanie a overenie párovania platieb</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -810,13 +825,13 @@
 ```</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozšírenie #3 — Ročné zúčtovanie služieb (DNR 4.3)</t>
+    <t xml:space="preserve">4.3 Ročné zúčtovanie služieb</t>
   </si>
   <si>
     <t xml:space="preserve">ROZŠÍRENIE Č. 3 — ROČNÉ ZÚČTOVANIE SLUŽIEB (DNR sekcia 4.3)
-== 4.3.1 Biznisový účel ==
+** 4.3.1 Biznisový účel **
 Raz ročne (za kalendárny rok január — december) sa vykoná finančné vyrovnanie medzi skutočnými nákladmi na služby (elektrina, voda/stočné, UK a TUV) a zálohami zaplatenými nájomcami počas roka. Výstupom je pre každého nájomcu individuálny PDF doklad „Ročné zúčtovanie" ukazujúci: ročné zálohy (koľko zaplatil), skutočná spotreba (koľko spotreboval), preplatok alebo nedoplatok.
-== 4.3.2 Zásadné rozhodnutia ==
+** 4.3.2 Zásadné rozhodnutia **
 • Obdobie: Vždy kalendárny rok (január — december).
 • Zadávanie celkových nákladov budovy: Manuálne po konci roka — admin zadá celkovú ročnú sumu za elektrinu, vodu/stočné, UK a TUV.
 • Druhy zúčtovaných služieb: Elektrina, voda/stočné, UK a TUV — všetky v jednom zúčtovaní (naraz).
@@ -832,7 +847,7 @@
 • Schvaľovanie: Admin si najprv pozrie sumárny prehľad všetkých nájomcov, prípadne ručne upraví jednotlivé položky a zvolí „Schváliť zúčtovanie". Až potom prebehne hromadná príprava PDF.
 • Oprava jednotlivého výsledku po vygenerovaní: Ak sa po vygenerovaní zúčtovania zistí chyba pri jednom nájomcovi, admin môže ručne upraviť hodnoty pre tohto konkrétneho zákazníka a vygenerovať mu opravené PDF. Ostatné zúčtovania sa neprepočítavajú. Bežne sa neočakáva, ide o ošetrenie výnimočných situácií. (v1.2)
 • Pripravený doklad preplatku/nedoplatku: Systém pripraví len informačný dokument „Ročné zúčtovanie" s číslami. Faktúry alebo dobropisy na vyrovnanie rieši klient mimo systém.
-== 4.3.3 Algoritmus výpočtu (príklad pre elektrinu) ==
+** 4.3.3 Algoritmus výpočtu (príklad pre elektrinu) **
 Vstupy: celkový ročný náklad budovy za elektrinu = 50 000 €. V budove je 20 priestorov (spolu 1 000 m²), z toho:
 • 5 priestorov s podružným meraním (dynamická položka v zmluve) — 300 m², skutočná spotreba 80 000 kWh.
 • 12 priestorov bez merania (fixná záloha v zmluve) — 550 m², bez údajov o spotrebe.
@@ -844,9 +859,9 @@
 25. Koeficient €/m² pre nemerané = zostatok / (550 + 50) m² = zostatok / 600 m².
 26. Náklad priestoru napr. 40 m² = 40 × koeficient.
 27. Preplatok/nedoplatok = zálohy zaplatené za rok − skutočný náklad.
-== Dospresnenie algoritmu v príprave ==
+** Dospresnenie algoritmu v príprave **
 Presný vzorec rozdelenia medzi merané a nemerané priestory (či sa jednotková cena počíta spoločne alebo zvlášť) má viacero možných variantov. Na začiatku prípravy prebehne 60—90 minútový analytický workshop s klientom, kde sa rozhodnutie zafixuje a odsúhlasí.
-== 4.3.4 Scenár použitia ==
+** 4.3.4 Scenár použitia **
 28. Admin v januári 2027 v module „Ročné zúčtovania" vytvorí nové zúčtovanie pre rok 2026.
 29. Systém predvyplní sumu všetkých platieb a spotreby z meraní za rok 2026.
 30. Admin zadá celkové ročné náklady budovy (elektrina, voda/stočné, UK a TUV).
@@ -856,11 +871,17 @@
 34. Zvolí „Pripraviť a odoslať PDF hromadne" — pre každú zmluvu vznikne individuálny PDF dokument a odošle sa e-mailom.
 35. Ak sa po vygenerovaní zistí chyba u konkrétneho nájomcu, admin ručne upraví jeho hodnoty a vygeneruje len jeho opravené PDF; ostatné zúčtovania sa neprepočítavajú. (v1.2)
 36. Klient (družstvo) prípadné preplatky/nedoplatky vyrovná mimo systém.
-== 4.3.5 Odhad pracnosti ==
-Ročné zúčtovanie služieb: 2 MD (kalkulačná logika, sumárny prehľad, formát PDF, hromadné pripravenie a odosielanie).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidencia ročného zúčtovania služieb v systéme</t>
+** Sumár akceptačných kritérií (z hlavných úloh) **
+• [4.3.1] V systéme existuje samostatný modul „Ročné zúčtovania", v ktorom je možné pre konkrétny kalendárny rok zaevidovať celkové ročné náklady budovy (elektrina, voda/stočné, UK, TUV).
+• [4.3.2] Pre každé zúčtovanie systém eviduje detail per zmluva, per priestor a per typ služby.
+• [4.3.3] Pre každý typ služby (elektrina, voda/stočné, UK, TUV) systém:
+• [4.3.4] Admin v module „Ročné zúčtovania" vytvorí nové zúčtovanie pre rok (napr. 2026).
+• [4.3.5] Pre každú zmluvu so záznamami v zúčtovaní systém vie vygenerovať individuálny PDF dokument „Ročné zúčtovanie".
+• [4.3.6] Po schválení zúčtovania admin spustí hromadnú akciu „Pripraviť a odoslať PDF hromadne".
+• [4.3.8] Pest test sada pokrýva všetky scenáre DNR 4.3.4 a edge cases z 4.3.2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3.1 Evidencia ročného zúčtovania služieb v systéme</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -901,7 +922,7 @@
 - Index `[annual_settlement_id, contract_id, service_type]`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Štruktúra údajov o vyúčtovaní per zmluva a priestor</t>
+    <t xml:space="preserve">4.3.2 Štruktúra údajov o vyúčtovaní per zmluva a priestor</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -928,7 +949,7 @@
 - `app/Enums/SettlementStatus.php` (draft/approved/sent).</t>
   </si>
   <si>
-    <t xml:space="preserve">Výpočtový engine ročného zúčtovania (kľúčový bod)</t>
+    <t xml:space="preserve">4.3.3 Výpočtový engine ročného zúčtovania (kľúčový bod)</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -1003,7 +1024,7 @@
 - Priestor správcu bez zmluvy: m² v deliteľi, ale `final_cost` ide na firmu (samostatný riadok bez contract_id alebo pole `building_overhead` v metadata).</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozhranie pre prípravu, kontrolu a schválenie zúčtovania</t>
+    <t xml:space="preserve">4.3.4 Rozhranie pre prípravu, kontrolu a schválenie zúčtovania</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -1036,7 +1057,7 @@
 - Po `approved`: úprava `final_cost` zakázaná (Policy `update`), zostáva otvorená iba akcia „Regenerovať jedno PDF" (Task 3.7).</t>
   </si>
   <si>
-    <t xml:space="preserve">PDF výstup ročného zúčtovania pre nájomcu</t>
+    <t xml:space="preserve">4.3.5 PDF výstup ročného zúčtovania pre nájomcu</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -1076,7 +1097,7 @@
 `public/css/settlement.css` (analógia k `invoice.css`).</t>
   </si>
   <si>
-    <t xml:space="preserve">Hromadné odoslanie ročných zúčtovaní e-mailom</t>
+    <t xml:space="preserve">4.3.6 Hromadné odoslanie ročných zúčtovaní e-mailom</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -1107,7 +1128,7 @@
 - Error handling per zmluva (log + zhrnutie v ActionResponse).</t>
   </si>
   <si>
-    <t xml:space="preserve">Audit log úprav a oprava jednotlivých zúčtovaní</t>
+    <t xml:space="preserve">4.3.7 Audit log úprav a oprava jednotlivých zúčtovaní</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
@@ -1146,7 +1167,7 @@
     <t xml:space="preserve">Low</t>
   </si>
   <si>
-    <t xml:space="preserve">Testovanie a overenie ročného zúčtovania</t>
+    <t xml:space="preserve">4.3.8 Testovanie a overenie ročného zúčtovania</t>
   </si>
   <si>
     <t xml:space="preserve">## Akceptačné kritériá
